--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1203,6 +1203,658 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980201</v>
+      </c>
+      <c r="C9" t="n">
+        <v>980201</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>980121</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>980121</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.173333</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>e8d66676d5e92195c37147293908215f4fcb16b386fddd83168197c0f8964d17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980202</v>
+      </c>
+      <c r="C10" t="n">
+        <v>980202</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>980121</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>980121</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.173333</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>f65bdaff032ac1b0ee204c86bf785cbf62d04e7dd347e0c7203886e38926d606</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>980203</v>
+      </c>
+      <c r="C11" t="n">
+        <v>980203</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>980122</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>980122</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4e73d8ab989465c6b6e6db77ffe643be156c0bcc3127e6097e93acc0c311bd97</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>980204</v>
+      </c>
+      <c r="C12" t="n">
+        <v>980204</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>980122</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>980122</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>56549d3bc1a4b7712c3d6defb97e324b1ec44992bec83189dc03ba171c0b1fa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>980205</v>
+      </c>
+      <c r="C13" t="n">
+        <v>980205</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>980123</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>980123</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>5cb55d5f0b0dd851e0b30ca0e8b724f05fc69a1240a75d2ad52a892ff769cf2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>980207</v>
+      </c>
+      <c r="C14" t="n">
+        <v>980207</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>980124</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2b1a4c96092251c8a66f286524bae05bd0ae73c0418484580a1103a4cac8a414</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>980206</v>
+      </c>
+      <c r="C15" t="n">
+        <v>980206</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>980124</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>b616ee9cf0376850c5d8d4744ef460c2cf3db10ed6d452fe95a90276591935e2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1855,6 +1855,100 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1000201</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10003</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1000110</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1000110</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>16e8386fd6066fdd900356ee1d6a8fec45ef653dd3818ffaeb263c72a1e7d64f</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1949,6 +1949,382 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1020202</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1020202</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1020121</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1020121</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>5b5e5788ab982863a046287f8674bb506a08db138e3d079bb5161401466d4790</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1020204</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1020204</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1020121</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1020121</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>bbc0d499a9eba2eab5ccd6250d85711fa003116b9222049fa13d5b425372fb35</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1020205</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1020205</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1020121</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1020121</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>de2c2775ebcb201535097cf8fedc6fffc6669e59ffa8e453acf5a4dc5df960c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1020201</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1020201</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1020121</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1020121</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>f97bbbbeb7bc383319fc7364ebdd2038536b0d90889175ef8bad690fc4b3b5ef</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -2325,6 +2325,288 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1030202</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1030202</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1030121</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1030121</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.09375</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>08313e432abc6d04e56fbf44b170388b3b6191ffb15abac9ea4d02ee759c440f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1030201</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1030201</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1030121</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1030121</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.09375</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>332d48387924567788c57bfd271afcfd8a07749fc1f8458f926c662f25eadbb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1030203</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1030203</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1030122</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1030122</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>069b2abf7d53155c525cef2b29329bcba15eefacfd89bd84e98142bd86c2f843</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -2607,6 +2607,570 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1040201</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1040201</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1040121|1040124</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1040121</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.307692</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.923077</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>172ba5fae3f99d4b3ab4f3261e03c998a122435132626403e3bbcf881044e8ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1040202</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1040202</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1040122|1040124</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1040122</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.323077</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>4281aa30493382a8172fd4f0bd6b2525ae9a6bb2c23b5a466d187f6fa2b0679d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1040204</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1040204</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1040122|1040124</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1040122</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.323077</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>92c9bae50e26e21d9e1740c9fb2c94f080f10c0806b57f258838164e1d7e875a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1040203</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1040203</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1040122|1040124</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1040122</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.323077</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>ce8bcd71466d7f1250b6b33d109b9d18ad9fe93d27b3ff6a5b0808757c54e01a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1040206</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1040206</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1040123|1040124</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1040123</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.692308</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1c7cd7a535dfcfb26a403383f8563dabcdcc39d766bb04c48db678e21c6260c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1040205</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1040205</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1040123|1040124</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1040123</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.692308</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>786366047ad1b743f5cb98102079707d9472d94da8dddbc4efd36edbcc1fc848</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -3171,6 +3171,370 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1060204</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1060204</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>11</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>27cc8087432063a0fb521d6ee2c3215f205b01698f32e5659941ba6c81585874</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1060202</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1060202</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>9</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2f3c43d2c53f62d040a9147f1b1f3264e2f3734e137ca9f19f97e9dba8047c03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1060201</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1060201</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>8</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>d85ff9f937de131f7a642f82c73c29366eead22fc38cc239ff5fb4b3620f0a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1060203</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1060203</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>ddd47d936105bdb11189838ccfe4c360b28ba4324694addeaa357a2ed6913588</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U33"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -3535,6 +3535,664 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1080202</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1080202</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1080120</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.093333</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>3bf1f9fdf1e6d766c220a0b6ab67e8662e08eb156684c61455e88b2feb24eb56</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1080201</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1080201</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1080120</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.093333</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>b41838e8e3949b9eb7e8fa4d011cc49ea9112d8b7912afc9b510a9b3150c5157</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1080204</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1080204</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1080120</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.093333</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>df138b6c46a435efe3bdd11aaa00382896e95fbb06b27b049a578046ca8b8344</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1080203</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1080203</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1080120</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.093333</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>e26e4475cff006e03c0886f166fdbf0a384f1f58d8ce7ad6891ecdf4dec7391f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1080205</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1080205</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1080123</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1080123</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0.833333</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>764677b6d7625223def1baa31961e01629ed3cff87c80214c1722b71f3ae0892</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1080206</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1080206</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1080123</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1080123</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0.833333</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>cf2c464bf6fc5dec93fd906cda1e5a2dd63d96b217753231c0f794fabb2be2d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1080207</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1080207</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1080124|1080125|1080126|1080127|1080128</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1080124</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.233333</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>ecbb70183d1c21d74a6023c8753f554a91346c56b0209674696834ddbdde66db</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U40"/>
+  <dimension ref="A1:U42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -4193,6 +4193,194 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1090352</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1090352</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1090381</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1090381</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>0a5beb1259e90ac335cd16387575bb30f2da5b5f0bba2c3c26719bb8024020b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1090351</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1090351</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1090381</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1090381</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>263571a258d76732b92eed539fe5bbe907952182074b90fb0a9cebe4775a5981</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -4381,6 +4381,194 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1100351</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1100351</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1100381</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1100381</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>39802b1becd4d2b2585fc367fbb8584dd29245ec5efda4ac5e02ca18a9045b34</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1100352</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1100352</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1100381</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1100381</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>c7f39dd121e1ba84d999da563dab2eb6bd82d810eb9e39d9ade1280f5340885a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:U46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -4569,6 +4569,194 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1110351</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1110351</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1110381</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1110381</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>df7c076f2b7a7df3e5554cc7069d766f5bf18ee192d7845514edddabcf9ef0a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1110352</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1110352</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1110381</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1110381</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>fbc29e16ac0abcb79ec537b38bcd8a54ac75629df845b8b20be8b4150a9678f8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U46"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -4757,6 +4757,194 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1120351</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1120351</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1120381</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1120381</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>8c8f418c38ed3dfd15f9c24bf4c862c37d1b86e0c9e1707d7f2fa2e86e0a091f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1120352</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1120352</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1120381</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1120381</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>b42fc6a2125c81acd49044e1778d5a31e425710c9eaaa24164c1171d3d4755eb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U48"/>
+  <dimension ref="A1:U50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -4945,6 +4945,194 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1130351</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1130351</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1130381</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1130381</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>45869fd358ef7a0ef896036c8ff914b3d9f44c058544b4cf20c23bab557a52e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1130352</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1130352</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1130381</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1130381</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>7581bdb28283176702cceb9519f7819bc4008ba565ce88032758801e9d0307ea</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1203,6 +1203,3936 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980201</v>
+      </c>
+      <c r="C9" t="n">
+        <v>980201</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>980121</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>980121</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.173333</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>e8d66676d5e92195c37147293908215f4fcb16b386fddd83168197c0f8964d17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980202</v>
+      </c>
+      <c r="C10" t="n">
+        <v>980202</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>980121</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>980121</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.173333</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>f65bdaff032ac1b0ee204c86bf785cbf62d04e7dd347e0c7203886e38926d606</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>980203</v>
+      </c>
+      <c r="C11" t="n">
+        <v>980203</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>980122</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>980122</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4e73d8ab989465c6b6e6db77ffe643be156c0bcc3127e6097e93acc0c311bd97</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>980204</v>
+      </c>
+      <c r="C12" t="n">
+        <v>980204</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>980122</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>980122</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>56549d3bc1a4b7712c3d6defb97e324b1ec44992bec83189dc03ba171c0b1fa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>980205</v>
+      </c>
+      <c r="C13" t="n">
+        <v>980205</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>980123</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>980123</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>5cb55d5f0b0dd851e0b30ca0e8b724f05fc69a1240a75d2ad52a892ff769cf2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>980207</v>
+      </c>
+      <c r="C14" t="n">
+        <v>980207</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>980124</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2b1a4c96092251c8a66f286524bae05bd0ae73c0418484580a1103a4cac8a414</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>980206</v>
+      </c>
+      <c r="C15" t="n">
+        <v>980206</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>980124</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>b616ee9cf0376850c5d8d4744ef460c2cf3db10ed6d452fe95a90276591935e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1000201</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10003</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Linked</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1000110</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1000110</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>16e8386fd6066fdd900356ee1d6a8fec45ef653dd3818ffaeb263c72a1e7d64f</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1020202</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1020202</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1020121</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1020121</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>5b5e5788ab982863a046287f8674bb506a08db138e3d079bb5161401466d4790</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1020204</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1020204</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1020121</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1020121</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>bbc0d499a9eba2eab5ccd6250d85711fa003116b9222049fa13d5b425372fb35</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1020205</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1020205</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1020121</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1020121</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>de2c2775ebcb201535097cf8fedc6fffc6669e59ffa8e453acf5a4dc5df960c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1020201</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1020201</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1020121</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1020121</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>f97bbbbeb7bc383319fc7364ebdd2038536b0d90889175ef8bad690fc4b3b5ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1030202</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1030202</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1030121</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1030121</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.09375</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>08313e432abc6d04e56fbf44b170388b3b6191ffb15abac9ea4d02ee759c440f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1030201</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1030201</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1030121</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1030121</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.09375</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>332d48387924567788c57bfd271afcfd8a07749fc1f8458f926c662f25eadbb9</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1030203</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1030203</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1030122</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1030122</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>069b2abf7d53155c525cef2b29329bcba15eefacfd89bd84e98142bd86c2f843</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1040201</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1040201</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1040121|1040124</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1040121</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.307692</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.923077</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>172ba5fae3f99d4b3ab4f3261e03c998a122435132626403e3bbcf881044e8ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1040202</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1040202</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1040122|1040124</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1040122</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.323077</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>4281aa30493382a8172fd4f0bd6b2525ae9a6bb2c23b5a466d187f6fa2b0679d</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1040204</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1040204</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1040122|1040124</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1040122</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.323077</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>92c9bae50e26e21d9e1740c9fb2c94f080f10c0806b57f258838164e1d7e875a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1040203</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1040203</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1040122|1040124</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1040122</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.323077</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>ce8bcd71466d7f1250b6b33d109b9d18ad9fe93d27b3ff6a5b0808757c54e01a</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1040206</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1040206</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1040123|1040124</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1040123</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.692308</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1c7cd7a535dfcfb26a403383f8563dabcdcc39d766bb04c48db678e21c6260c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1040205</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1040205</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1040123|1040124</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1040123</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.692308</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1.333333</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>786366047ad1b743f5cb98102079707d9472d94da8dddbc4efd36edbcc1fc848</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1060204</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1060204</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>11</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>27cc8087432063a0fb521d6ee2c3215f205b01698f32e5659941ba6c81585874</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1060202</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1060202</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>9</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2f3c43d2c53f62d040a9147f1b1f3264e2f3734e137ca9f19f97e9dba8047c03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1060201</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1060201</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>8</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>d85ff9f937de131f7a642f82c73c29366eead22fc38cc239ff5fb4b3620f0a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1060203</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1060203</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>ddd47d936105bdb11189838ccfe4c360b28ba4324694addeaa357a2ed6913588</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1080202</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1080202</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1080120</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.093333</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>3bf1f9fdf1e6d766c220a0b6ab67e8662e08eb156684c61455e88b2feb24eb56</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1080201</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1080201</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1080120</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.093333</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>b41838e8e3949b9eb7e8fa4d011cc49ea9112d8b7912afc9b510a9b3150c5157</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1080204</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1080204</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1080120</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.093333</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>df138b6c46a435efe3bdd11aaa00382896e95fbb06b27b049a578046ca8b8344</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>1080203</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1080203</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1080120</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.093333</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>e26e4475cff006e03c0886f166fdbf0a384f1f58d8ce7ad6891ecdf4dec7391f</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1080205</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1080205</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1080123</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1080123</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0.833333</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>764677b6d7625223def1baa31961e01629ed3cff87c80214c1722b71f3ae0892</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1080206</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1080206</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1080123</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1080123</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.266667</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0.833333</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>cf2c464bf6fc5dec93fd906cda1e5a2dd63d96b217753231c0f794fabb2be2d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1080207</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1080207</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1080124|1080125|1080126|1080127|1080128</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1080124</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.233333</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>ecbb70183d1c21d74a6023c8753f554a91346c56b0209674696834ddbdde66db</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1090352</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1090352</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1090381</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1090381</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>0a5beb1259e90ac335cd16387575bb30f2da5b5f0bba2c3c26719bb8024020b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1090351</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1090351</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1090381</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1090381</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>263571a258d76732b92eed539fe5bbe907952182074b90fb0a9cebe4775a5981</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1100351</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1100351</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1100381</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1100381</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>39802b1becd4d2b2585fc367fbb8584dd29245ec5efda4ac5e02ca18a9045b34</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1100352</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1100352</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1100381</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1100381</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>c7f39dd121e1ba84d999da563dab2eb6bd82d810eb9e39d9ade1280f5340885a</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1110351</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1110351</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1110381</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1110381</v>
+      </c>
+      <c r="H45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>df7c076f2b7a7df3e5554cc7069d766f5bf18ee192d7845514edddabcf9ef0a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1110352</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1110352</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1110381</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1110381</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>fbc29e16ac0abcb79ec537b38bcd8a54ac75629df845b8b20be8b4150a9678f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1120351</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1120351</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1120381</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1120381</v>
+      </c>
+      <c r="H47" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>8c8f418c38ed3dfd15f9c24bf4c862c37d1b86e0c9e1707d7f2fa2e86e0a091f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1120352</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1120352</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1120381</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1120381</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>b42fc6a2125c81acd49044e1778d5a31e425710c9eaaa24164c1171d3d4755eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1130351</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1130351</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1130381</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1130381</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>45869fd358ef7a0ef896036c8ff914b3d9f44c058544b4cf20c23bab557a52e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1130352</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1130352</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1130381</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1130381</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Depart</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>7581bdb28283176702cceb9519f7819bc4008ba565ce88032758801e9d0307ea</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Summon, Memosprite, SharedActor" promptTitle="LinkedUnitKind enum" prompt="Select a value from the dropdown." type="list">

--- a/config/data/LinkedUnitDefinition.xlsx
+++ b/config/data/LinkedUnitDefinition.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LinkedUnitDefinition" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedUnitDefinition" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -556,12 +556,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>@scope</t>
+          <t>@groups</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>77b0bd392776be64</t>
+          <t>77adc4c80b4e70d2</t>
         </is>
       </c>
     </row>
@@ -899,107 +899,107 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>#scope</t>
+          <t>#groups</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="R5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="S5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="T5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="U5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
     </row>
@@ -1110,11 +1110,15 @@
       <c r="U7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>24505</v>
-      </c>
-      <c r="C8" t="n">
-        <v>20005</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24505</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>20005</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1131,11 +1135,15 @@
           <t>24610</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>24610</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>24610</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1204,11 +1212,15 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>980201</v>
-      </c>
-      <c r="C9" t="n">
-        <v>980201</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>980201</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>980201</t>
+        </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1225,11 +1237,15 @@
           <t>980121</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>980121</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>980121</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1298,11 +1314,15 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>980202</v>
-      </c>
-      <c r="C10" t="n">
-        <v>980202</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>980202</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>980202</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1319,11 +1339,15 @@
           <t>980121</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>980121</v>
-      </c>
-      <c r="H10" t="n">
-        <v>9</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>980121</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1392,11 +1416,15 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>980203</v>
-      </c>
-      <c r="C11" t="n">
-        <v>980203</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>980203</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>980203</t>
+        </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1413,11 +1441,15 @@
           <t>980122</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>980122</v>
-      </c>
-      <c r="H11" t="n">
-        <v>10</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>980122</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1486,11 +1518,15 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>980204</v>
-      </c>
-      <c r="C12" t="n">
-        <v>980204</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>980204</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>980204</t>
+        </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1507,11 +1543,15 @@
           <t>980122</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>980122</v>
-      </c>
-      <c r="H12" t="n">
-        <v>11</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>980122</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1580,11 +1620,15 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>980205</v>
-      </c>
-      <c r="C13" t="n">
-        <v>980205</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>980205</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>980205</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1601,11 +1645,15 @@
           <t>980123</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>980123</v>
-      </c>
-      <c r="H13" t="n">
-        <v>12</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>980123</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1674,11 +1722,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>980207</v>
-      </c>
-      <c r="C14" t="n">
-        <v>980207</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>980207</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>980207</t>
+        </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1695,8 +1747,10 @@
           <t>980124</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>14</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1765,11 +1819,15 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>980206</v>
-      </c>
-      <c r="C15" t="n">
-        <v>980206</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>980206</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>980206</t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1786,8 +1844,10 @@
           <t>980124</t>
         </is>
       </c>
-      <c r="H15" t="n">
-        <v>13</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1856,11 +1916,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>1000201</v>
-      </c>
-      <c r="C16" t="n">
-        <v>10003</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1000201</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1877,11 +1941,15 @@
           <t>1000110</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>1000110</v>
-      </c>
-      <c r="H16" t="n">
-        <v>8</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1000110</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1950,11 +2018,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>1020202</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1020202</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1040201</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1040201</t>
+        </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1968,14 +2040,18 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1020121</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1020121</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
+          <t>1040121|1040124</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1040121</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1984,7 +2060,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.307692</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1994,7 +2070,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.923077</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2019,7 +2095,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -2039,16 +2115,20 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>5b5e5788ab982863a046287f8674bb506a08db138e3d079bb5161401466d4790</t>
+          <t>172ba5fae3f99d4b3ab4f3261e03c998a122435132626403e3bbcf881044e8ac</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>1020204</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1020204</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1040202</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1040202</t>
+        </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2062,14 +2142,18 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1020121</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1020121</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4</v>
+          <t>1040122|1040124</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1040122</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2078,7 +2162,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.323077</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2088,7 +2172,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.333333</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2133,16 +2217,20 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>bbc0d499a9eba2eab5ccd6250d85711fa003116b9222049fa13d5b425372fb35</t>
+          <t>4281aa30493382a8172fd4f0bd6b2525ae9a6bb2c23b5a466d187f6fa2b0679d</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>1020205</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1020205</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1040204</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1040204</t>
+        </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2156,14 +2244,18 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1020121</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1020121</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5</v>
+          <t>1040122|1040124</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1040122</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2172,7 +2264,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.323077</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2182,7 +2274,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.333333</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2227,16 +2319,20 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>de2c2775ebcb201535097cf8fedc6fffc6669e59ffa8e453acf5a4dc5df960c7</t>
+          <t>92c9bae50e26e21d9e1740c9fb2c94f080f10c0806b57f258838164e1d7e875a</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>1020201</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1020201</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1040203</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1040203</t>
+        </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2250,14 +2346,18 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1020121</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1020121</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1</v>
+          <t>1040122|1040124</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1040122</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2266,7 +2366,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.323077</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2276,7 +2376,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.333333</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2321,16 +2421,20 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>f97bbbbeb7bc383319fc7364ebdd2038536b0d90889175ef8bad690fc4b3b5ef</t>
+          <t>ce8bcd71466d7f1250b6b33d109b9d18ad9fe93d27b3ff6a5b0808757c54e01a</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>1030202</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1030202</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1040206</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1040206</t>
+        </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2344,14 +2448,18 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1030121</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1030121</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5</v>
+          <t>1040123|1040124</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1040123</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2360,7 +2468,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.09375</t>
+          <t>0.692308</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2370,7 +2478,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.333333</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2415,16 +2523,20 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>08313e432abc6d04e56fbf44b170388b3b6191ffb15abac9ea4d02ee759c440f</t>
+          <t>1c7cd7a535dfcfb26a403383f8563dabcdcc39d766bb04c48db678e21c6260c3</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>1030201</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1030201</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1040205</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1040205</t>
+        </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2438,14 +2550,18 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1030121</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1030121</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1</v>
+          <t>1040123|1040124</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1040123</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2454,7 +2570,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.09375</t>
+          <t>0.692308</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2464,7 +2580,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.333333</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2509,16 +2625,20 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>332d48387924567788c57bfd271afcfd8a07749fc1f8458f926c662f25eadbb9</t>
+          <t>786366047ad1b743f5cb98102079707d9472d94da8dddbc4efd36edbcc1fc848</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>1030203</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1030203</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1060204</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1060204</t>
+        </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2532,14 +2652,13 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1030122</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1030122</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4</v>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2548,7 +2667,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2583,7 +2702,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2603,16 +2722,20 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>069b2abf7d53155c525cef2b29329bcba15eefacfd89bd84e98142bd86c2f843</t>
+          <t>27cc8087432063a0fb521d6ee2c3215f205b01698f32e5659941ba6c81585874</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>1040201</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1040201</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1060202</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1060202</t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2626,14 +2749,13 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1040121|1040124</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1040121</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2642,7 +2764,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.307692</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2652,7 +2774,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.923077</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2677,7 +2799,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2697,16 +2819,20 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>172ba5fae3f99d4b3ab4f3261e03c998a122435132626403e3bbcf881044e8ac</t>
+          <t>2f3c43d2c53f62d040a9147f1b1f3264e2f3734e137ca9f19f97e9dba8047c03</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>1040202</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1040202</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1060201</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1060201</t>
+        </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2720,14 +2846,13 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1040122|1040124</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>1040122</v>
-      </c>
-      <c r="H25" t="n">
-        <v>5</v>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2736,7 +2861,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.323077</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2746,7 +2871,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.333333</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2771,7 +2896,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2791,16 +2916,20 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>4281aa30493382a8172fd4f0bd6b2525ae9a6bb2c23b5a466d187f6fa2b0679d</t>
+          <t>d85ff9f937de131f7a642f82c73c29366eead22fc38cc239ff5fb4b3620f0a7a</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>1040204</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1040204</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1060203</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1060203</t>
+        </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2814,14 +2943,13 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1040122|1040124</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1040122</v>
-      </c>
-      <c r="H26" t="n">
-        <v>5</v>
+          <t>1060108</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2830,7 +2958,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.323077</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2840,7 +2968,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1.333333</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2865,7 +2993,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2885,16 +3013,20 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>92c9bae50e26e21d9e1740c9fb2c94f080f10c0806b57f258838164e1d7e875a</t>
+          <t>ddd47d936105bdb11189838ccfe4c360b28ba4324694addeaa357a2ed6913588</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>1040203</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1040203</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1080202</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1080202</t>
+        </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2908,14 +3040,18 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1040122|1040124</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1040122</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1</v>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080120</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2924,7 +3060,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.323077</t>
+          <t>0.093333</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2934,7 +3070,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1.333333</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2979,16 +3115,20 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>ce8bcd71466d7f1250b6b33d109b9d18ad9fe93d27b3ff6a5b0808757c54e01a</t>
+          <t>3bf1f9fdf1e6d766c220a0b6ab67e8662e08eb156684c61455e88b2feb24eb56</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
-        <v>1040206</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1040206</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1080201</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1080201</t>
+        </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3002,14 +3142,18 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1040123|1040124</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1040123</v>
-      </c>
-      <c r="H28" t="n">
-        <v>5</v>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080120</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -3018,7 +3162,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.692308</t>
+          <t>0.093333</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3028,7 +3172,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>1.333333</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3053,7 +3197,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3073,16 +3217,20 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>1c7cd7a535dfcfb26a403383f8563dabcdcc39d766bb04c48db678e21c6260c3</t>
+          <t>b41838e8e3949b9eb7e8fa4d011cc49ea9112d8b7912afc9b510a9b3150c5157</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
-        <v>1040205</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1040205</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1080204</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1080204</t>
+        </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3096,14 +3244,18 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1040123|1040124</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1040123</v>
-      </c>
-      <c r="H29" t="n">
-        <v>1</v>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080120</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -3112,7 +3264,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.692308</t>
+          <t>0.093333</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3122,7 +3274,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.333333</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3147,7 +3299,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3167,16 +3319,20 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>786366047ad1b743f5cb98102079707d9472d94da8dddbc4efd36edbcc1fc848</t>
+          <t>df138b6c46a435efe3bdd11aaa00382896e95fbb06b27b049a578046ca8b8344</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>1060204</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1060204</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1080203</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1080203</t>
+        </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3190,11 +3346,18 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1060108</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>11</v>
+          <t>1080120|1080121|1080122</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080120</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -3203,7 +3366,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.093333</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3238,7 +3401,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3258,16 +3421,20 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>27cc8087432063a0fb521d6ee2c3215f205b01698f32e5659941ba6c81585874</t>
+          <t>e26e4475cff006e03c0886f166fdbf0a384f1f58d8ce7ad6891ecdf4dec7391f</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
-        <v>1060202</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1060202</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1080205</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1080205</t>
+        </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3281,11 +3448,18 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1060108</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>9</v>
+          <t>1080123</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080123</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -3294,7 +3468,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.266667</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3304,7 +3478,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.833333</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3329,7 +3503,7 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3349,16 +3523,20 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2f3c43d2c53f62d040a9147f1b1f3264e2f3734e137ca9f19f97e9dba8047c03</t>
+          <t>764677b6d7625223def1baa31961e01629ed3cff87c80214c1722b71f3ae0892</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
-        <v>1060201</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1060201</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1080206</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1080206</t>
+        </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3372,11 +3550,18 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1060108</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>8</v>
+          <t>1080123</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080123</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -3385,7 +3570,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.266667</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3395,7 +3580,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.833333</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3420,7 +3605,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3440,16 +3625,20 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>d85ff9f937de131f7a642f82c73c29366eead22fc38cc239ff5fb4b3620f0a7a</t>
+          <t>cf2c464bf6fc5dec93fd906cda1e5a2dd63d96b217753231c0f794fabb2be2d3</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
-        <v>1060203</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1060203</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1080207</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1080207</t>
+        </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3463,11 +3652,18 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1060108</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>10</v>
+          <t>1080124|1080125|1080126|1080127|1080128</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080124</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -3476,7 +3672,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0.233333</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3511,7 +3707,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3531,16 +3727,20 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>ddd47d936105bdb11189838ccfe4c360b28ba4324694addeaa357a2ed6913588</t>
+          <t>ecbb70183d1c21d74a6023c8753f554a91346c56b0209674696834ddbdde66db</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
-        <v>1080202</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1080202</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1090352</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1090352</t>
+        </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3554,14 +3754,18 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1080120|1080121|1080122</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>1080120</v>
-      </c>
-      <c r="H34" t="n">
-        <v>2</v>
+          <t>1090381</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1090381</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -3570,7 +3774,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.093333</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3580,7 +3784,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3605,7 +3809,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3625,16 +3829,20 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>3bf1f9fdf1e6d766c220a0b6ab67e8662e08eb156684c61455e88b2feb24eb56</t>
+          <t>0a5beb1259e90ac335cd16387575bb30f2da5b5f0bba2c3c26719bb8024020b7</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
-        <v>1080201</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1080201</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1090351</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1090351</t>
+        </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3648,14 +3856,18 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1080120|1080121|1080122</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>1080120</v>
-      </c>
-      <c r="H35" t="n">
-        <v>1</v>
+          <t>1090381</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1090381</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -3664,7 +3876,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.093333</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3674,7 +3886,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3699,7 +3911,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3719,16 +3931,20 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>b41838e8e3949b9eb7e8fa4d011cc49ea9112d8b7912afc9b510a9b3150c5157</t>
+          <t>263571a258d76732b92eed539fe5bbe907952182074b90fb0a9cebe4775a5981</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
-        <v>1080204</v>
-      </c>
-      <c r="C36" t="n">
-        <v>1080204</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1100351</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1100351</t>
+        </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3742,14 +3958,18 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1080120|1080121|1080122</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1080120</v>
-      </c>
-      <c r="H36" t="n">
-        <v>5</v>
+          <t>1100381</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1100381</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -3758,7 +3978,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.093333</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3768,7 +3988,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3793,7 +4013,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3813,16 +4033,20 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>df138b6c46a435efe3bdd11aaa00382896e95fbb06b27b049a578046ca8b8344</t>
+          <t>39802b1becd4d2b2585fc367fbb8584dd29245ec5efda4ac5e02ca18a9045b34</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
-        <v>1080203</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1080203</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1100352</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1100352</t>
+        </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3836,14 +4060,18 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1080120|1080121|1080122</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1080120</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4</v>
+          <t>1100381</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1100381</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -3852,7 +4080,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.093333</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3862,7 +4090,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3887,7 +4115,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3907,16 +4135,20 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>e26e4475cff006e03c0886f166fdbf0a384f1f58d8ce7ad6891ecdf4dec7391f</t>
+          <t>c7f39dd121e1ba84d999da563dab2eb6bd82d810eb9e39d9ade1280f5340885a</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
-        <v>1080205</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1080205</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1110351</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1110351</t>
+        </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3930,14 +4162,18 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1080123</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1080123</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
+          <t>1110381</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1110381</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -3946,7 +4182,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.266667</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3956,7 +4192,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.833333</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3981,7 +4217,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4001,16 +4237,20 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>764677b6d7625223def1baa31961e01629ed3cff87c80214c1722b71f3ae0892</t>
+          <t>df7c076f2b7a7df3e5554cc7069d766f5bf18ee192d7845514edddabcf9ef0a7</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
-        <v>1080206</v>
-      </c>
-      <c r="C39" t="n">
-        <v>1080206</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1110352</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1110352</t>
+        </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4024,14 +4264,18 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1080123</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>1080123</v>
-      </c>
-      <c r="H39" t="n">
-        <v>5</v>
+          <t>1110381</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1110381</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -4040,7 +4284,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.266667</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -4050,7 +4294,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.833333</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4075,7 +4319,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>120</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4095,16 +4339,20 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>cf2c464bf6fc5dec93fd906cda1e5a2dd63d96b217753231c0f794fabb2be2d3</t>
+          <t>fbc29e16ac0abcb79ec537b38bcd8a54ac75629df845b8b20be8b4150a9678f8</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
-        <v>1080207</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1080207</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1120351</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1120351</t>
+        </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4118,14 +4366,18 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1080124|1080125|1080126|1080127|1080128</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>1080124</v>
-      </c>
-      <c r="H40" t="n">
-        <v>5</v>
+          <t>1120381</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1120381</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -4134,7 +4386,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.233333</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4144,7 +4396,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4189,16 +4441,20 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>ecbb70183d1c21d74a6023c8753f554a91346c56b0209674696834ddbdde66db</t>
+          <t>8c8f418c38ed3dfd15f9c24bf4c862c37d1b86e0c9e1707d7f2fa2e86e0a091f</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
-        <v>1090352</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1090352</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1120352</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1120352</t>
+        </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4212,14 +4468,18 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1090381</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1090381</v>
-      </c>
-      <c r="H41" t="n">
-        <v>4</v>
+          <t>1120381</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1120381</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -4283,16 +4543,20 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0a5beb1259e90ac335cd16387575bb30f2da5b5f0bba2c3c26719bb8024020b7</t>
+          <t>b42fc6a2125c81acd49044e1778d5a31e425710c9eaaa24164c1171d3d4755eb</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
-        <v>1090351</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1090351</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1130351</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1130351</t>
+        </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4306,14 +4570,18 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1090381</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>1090381</v>
-      </c>
-      <c r="H42" t="n">
-        <v>2</v>
+          <t>1130381</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1130381</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -4377,16 +4645,20 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>263571a258d76732b92eed539fe5bbe907952182074b90fb0a9cebe4775a5981</t>
+          <t>45869fd358ef7a0ef896036c8ff914b3d9f44c058544b4cf20c23bab557a52e3</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
-        <v>1100351</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1100351</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1130352</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1130352</t>
+        </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4400,14 +4672,18 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1100381</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>1100381</v>
-      </c>
-      <c r="H43" t="n">
-        <v>2</v>
+          <t>1130381</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1130381</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -4471,16 +4747,16 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>39802b1becd4d2b2585fc367fbb8584dd29245ec5efda4ac5e02ca18a9045b34</t>
+          <t>7581bdb28283176702cceb9519f7819bc4008ba565ce88032758801e9d0307ea</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
-        <v>1100352</v>
+        <v>1020202</v>
       </c>
       <c r="C44" t="n">
-        <v>1100352</v>
+        <v>1020202</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4494,14 +4770,14 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1100381</t>
+          <t>1020121</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1100381</v>
+        <v>1020121</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -4510,7 +4786,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4520,7 +4796,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4545,7 +4821,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4565,16 +4841,16 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>c7f39dd121e1ba84d999da563dab2eb6bd82d810eb9e39d9ade1280f5340885a</t>
+          <t>5b5e5788ab982863a046287f8674bb506a08db138e3d079bb5161401466d4790</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
-        <v>1110351</v>
+        <v>1020204</v>
       </c>
       <c r="C45" t="n">
-        <v>1110351</v>
+        <v>1020204</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4588,14 +4864,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1110381</t>
+          <t>1020121</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1110381</v>
+        <v>1020121</v>
       </c>
       <c r="H45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -4604,7 +4880,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4614,7 +4890,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4639,7 +4915,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4659,16 +4935,16 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>df7c076f2b7a7df3e5554cc7069d766f5bf18ee192d7845514edddabcf9ef0a7</t>
+          <t>bbc0d499a9eba2eab5ccd6250d85711fa003116b9222049fa13d5b425372fb35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
-        <v>1110352</v>
+        <v>1020205</v>
       </c>
       <c r="C46" t="n">
-        <v>1110352</v>
+        <v>1020205</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4682,14 +4958,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1110381</t>
+          <t>1020121</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1110381</v>
+        <v>1020121</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -4698,7 +4974,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4708,7 +4984,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4733,7 +5009,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4753,16 +5029,16 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>fbc29e16ac0abcb79ec537b38bcd8a54ac75629df845b8b20be8b4150a9678f8</t>
+          <t>de2c2775ebcb201535097cf8fedc6fffc6669e59ffa8e453acf5a4dc5df960c7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1120351</v>
+        <v>1020201</v>
       </c>
       <c r="C47" t="n">
-        <v>1120351</v>
+        <v>1020201</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4776,14 +5052,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1120381</t>
+          <t>1020121</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1120381</v>
+        <v>1020121</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -4792,7 +5068,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4802,7 +5078,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4827,7 +5103,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>100</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4847,16 +5123,16 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>8c8f418c38ed3dfd15f9c24bf4c862c37d1b86e0c9e1707d7f2fa2e86e0a091f</t>
+          <t>f97bbbbeb7bc383319fc7364ebdd2038536b0d90889175ef8bad690fc4b3b5ef</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1120352</v>
+        <v>1030202</v>
       </c>
       <c r="C48" t="n">
-        <v>1120352</v>
+        <v>1030202</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4870,14 +5146,14 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1120381</t>
+          <t>1030121</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1120381</v>
+        <v>1030121</v>
       </c>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -4886,7 +5162,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.09375</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4896,7 +5172,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4921,7 +5197,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4941,16 +5217,16 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>b42fc6a2125c81acd49044e1778d5a31e425710c9eaaa24164c1171d3d4755eb</t>
+          <t>08313e432abc6d04e56fbf44b170388b3b6191ffb15abac9ea4d02ee759c440f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1130351</v>
+        <v>1030201</v>
       </c>
       <c r="C49" t="n">
-        <v>1130351</v>
+        <v>1030201</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4964,14 +5240,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1130381</t>
+          <t>1030121</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1130381</v>
+        <v>1030121</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -4980,7 +5256,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.09375</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4990,7 +5266,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5015,7 +5291,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>144</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5035,16 +5311,16 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>45869fd358ef7a0ef896036c8ff914b3d9f44c058544b4cf20c23bab557a52e3</t>
+          <t>332d48387924567788c57bfd271afcfd8a07749fc1f8458f926c662f25eadbb9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1130352</v>
+        <v>1030203</v>
       </c>
       <c r="C50" t="n">
-        <v>1130352</v>
+        <v>1030203</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5058,11 +5334,11 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1130381</t>
+          <t>1030122</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1130381</v>
+        <v>1030122</v>
       </c>
       <c r="H50" t="n">
         <v>4</v>
@@ -5074,7 +5350,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5084,7 +5360,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5109,7 +5385,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>143</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5129,7 +5405,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>7581bdb28283176702cceb9519f7819bc4008ba565ce88032758801e9d0307ea</t>
+          <t>069b2abf7d53155c525cef2b29329bcba15eefacfd89bd84e98142bd86c2f843</t>
         </is>
       </c>
     </row>
